--- a/Output/effect_size.xlsx
+++ b/Output/effect_size.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>food_group_Food Colour/Flavour and Baking Additivies</t>
+          <t>food_group_Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>food_group_Sweet Snacks/Baked Foods</t>
+          <t>food_group_Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
     </row>
